--- a/output/pdf_financials_xlsx/PLTO.xlsx
+++ b/output/pdf_financials_xlsx/PLTO.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.327425</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.057462</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.327425</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.057462</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.327425</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.057462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/PLTO.xlsx
+++ b/output/pdf_financials_xlsx/PLTO.xlsx
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005382</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00479</v>
       </c>
     </row>
     <row r="102">
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.04491</v>
+        <v>0.039528</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.048181</v>
+        <v>0.043391</v>
       </c>
     </row>
     <row r="107">
@@ -2664,7 +2664,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>-0.005382</v>
       </c>
